--- a/data/nzd0045/nzd0045.xlsx
+++ b/data/nzd0045/nzd0045.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O530"/>
+  <dimension ref="A1:O531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27472,6 +27472,57 @@
         <v>371.33</v>
       </c>
       <c r="O530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>399.62</v>
+      </c>
+      <c r="C531" t="n">
+        <v>407.97</v>
+      </c>
+      <c r="D531" t="n">
+        <v>398.7</v>
+      </c>
+      <c r="E531" t="n">
+        <v>396.26</v>
+      </c>
+      <c r="F531" t="n">
+        <v>392.38</v>
+      </c>
+      <c r="G531" t="n">
+        <v>393.41</v>
+      </c>
+      <c r="H531" t="n">
+        <v>393.33</v>
+      </c>
+      <c r="I531" t="n">
+        <v>392.82</v>
+      </c>
+      <c r="J531" t="n">
+        <v>394.45</v>
+      </c>
+      <c r="K531" t="n">
+        <v>380.73</v>
+      </c>
+      <c r="L531" t="n">
+        <v>375.2</v>
+      </c>
+      <c r="M531" t="n">
+        <v>376.99</v>
+      </c>
+      <c r="N531" t="n">
+        <v>369.26</v>
+      </c>
+      <c r="O531" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27488,7 +27539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B534"/>
+  <dimension ref="A1:B535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32831,6 +32882,16 @@
       </c>
       <c r="B534" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -32999,28 +33060,28 @@
         <v>0.1432</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1456501651437984</v>
+        <v>0.1446018130926982</v>
       </c>
       <c r="J2" t="n">
+        <v>530</v>
+      </c>
+      <c r="K2" t="n">
         <v>529</v>
       </c>
-      <c r="K2" t="n">
-        <v>528</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.05447970921479106</v>
+        <v>0.053910136547902</v>
       </c>
       <c r="M2" t="n">
-        <v>3.424803951848026</v>
+        <v>3.424113617190299</v>
       </c>
       <c r="N2" t="n">
-        <v>21.23831562666454</v>
+        <v>21.21374612830157</v>
       </c>
       <c r="O2" t="n">
-        <v>4.608504706156276</v>
+        <v>4.605838265538812</v>
       </c>
       <c r="P2" t="n">
-        <v>398.6773072334443</v>
+        <v>398.6877223410709</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33081,28 +33142,28 @@
         <v>0.1717</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1345894210464192</v>
+        <v>0.1337543924201816</v>
       </c>
       <c r="J3" t="n">
+        <v>530</v>
+      </c>
+      <c r="K3" t="n">
         <v>529</v>
       </c>
-      <c r="K3" t="n">
-        <v>528</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.04986801280652686</v>
+        <v>0.04944921410815128</v>
       </c>
       <c r="M3" t="n">
-        <v>3.359523162530915</v>
+        <v>3.358594629453658</v>
       </c>
       <c r="N3" t="n">
-        <v>19.90883111081609</v>
+        <v>19.88107987391241</v>
       </c>
       <c r="O3" t="n">
-        <v>4.461931320719324</v>
+        <v>4.458820457689725</v>
       </c>
       <c r="P3" t="n">
-        <v>406.7288868051202</v>
+        <v>406.7371825994618</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33159,28 +33220,28 @@
         <v>0.1431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.135881969363336</v>
+        <v>0.1349024006287672</v>
       </c>
       <c r="J4" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K4" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08353422201716865</v>
+        <v>0.08265326441199916</v>
       </c>
       <c r="M4" t="n">
-        <v>2.494184066788613</v>
+        <v>2.495322696789808</v>
       </c>
       <c r="N4" t="n">
-        <v>11.66437031687616</v>
+        <v>11.65593237096508</v>
       </c>
       <c r="O4" t="n">
-        <v>3.41531408758787</v>
+        <v>3.414078553719155</v>
       </c>
       <c r="P4" t="n">
-        <v>397.8219103510796</v>
+        <v>397.8316493789605</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33237,28 +33298,28 @@
         <v>0.1071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1576021382475794</v>
+        <v>0.1556170823663185</v>
       </c>
       <c r="J5" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K5" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1399082594130876</v>
+        <v>0.1366189384864199</v>
       </c>
       <c r="M5" t="n">
-        <v>2.174903031690964</v>
+        <v>2.181514515957506</v>
       </c>
       <c r="N5" t="n">
-        <v>8.792481194508683</v>
+        <v>8.831618533940867</v>
       </c>
       <c r="O5" t="n">
-        <v>2.965211829618363</v>
+        <v>2.971803919161032</v>
       </c>
       <c r="P5" t="n">
-        <v>397.5674947492346</v>
+        <v>397.5872304899649</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33315,28 +33376,28 @@
         <v>0.1192</v>
       </c>
       <c r="I6" t="n">
-        <v>0.110390601622933</v>
+        <v>0.1076205761402559</v>
       </c>
       <c r="J6" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K6" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05316260700436459</v>
+        <v>0.05044125859840631</v>
       </c>
       <c r="M6" t="n">
-        <v>2.785162897261969</v>
+        <v>2.797133147940867</v>
       </c>
       <c r="N6" t="n">
-        <v>12.49738488953335</v>
+        <v>12.58231926130612</v>
       </c>
       <c r="O6" t="n">
-        <v>3.535164054118754</v>
+        <v>3.547156503638671</v>
       </c>
       <c r="P6" t="n">
-        <v>397.0825616758558</v>
+        <v>397.1101017089896</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33393,28 +33454,28 @@
         <v>0.1403</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1676448805357607</v>
+        <v>0.1641055435332991</v>
       </c>
       <c r="J7" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K7" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08305040421818577</v>
+        <v>0.07943170113935161</v>
       </c>
       <c r="M7" t="n">
-        <v>3.370170665576476</v>
+        <v>3.377637401409119</v>
       </c>
       <c r="N7" t="n">
-        <v>17.86776030736279</v>
+        <v>18.01120664609445</v>
       </c>
       <c r="O7" t="n">
-        <v>4.22702736061204</v>
+        <v>4.243961197524602</v>
       </c>
       <c r="P7" t="n">
-        <v>398.7217308212844</v>
+        <v>398.7569194716881</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33471,28 +33532,28 @@
         <v>0.1456</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1255659465099952</v>
+        <v>0.1222524925920776</v>
       </c>
       <c r="J8" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K8" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03768988773275073</v>
+        <v>0.03570707133963069</v>
       </c>
       <c r="M8" t="n">
-        <v>3.672153787702866</v>
+        <v>3.679231018205187</v>
       </c>
       <c r="N8" t="n">
-        <v>23.18033824022096</v>
+        <v>23.29186958449125</v>
       </c>
       <c r="O8" t="n">
-        <v>4.814596373552092</v>
+        <v>4.826165101246667</v>
       </c>
       <c r="P8" t="n">
-        <v>399.132022341855</v>
+        <v>399.1649652267697</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33549,28 +33610,28 @@
         <v>0.1405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09944057531932478</v>
+        <v>0.09634460352240237</v>
       </c>
       <c r="J9" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K9" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01979483549632544</v>
+        <v>0.01859063833938213</v>
       </c>
       <c r="M9" t="n">
-        <v>3.974398756605139</v>
+        <v>3.981499999811406</v>
       </c>
       <c r="N9" t="n">
-        <v>28.19539347644151</v>
+        <v>28.27774901776437</v>
       </c>
       <c r="O9" t="n">
-        <v>5.309933471941199</v>
+        <v>5.317682673661937</v>
       </c>
       <c r="P9" t="n">
-        <v>398.707918532952</v>
+        <v>398.738699176091</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33627,28 +33688,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06130082735971201</v>
+        <v>0.05828812031309059</v>
       </c>
       <c r="J10" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K10" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007767069747580346</v>
+        <v>0.00702364589030724</v>
       </c>
       <c r="M10" t="n">
-        <v>4.173009475266124</v>
+        <v>4.18225241108039</v>
       </c>
       <c r="N10" t="n">
-        <v>27.64234716867925</v>
+        <v>27.71855289489756</v>
       </c>
       <c r="O10" t="n">
-        <v>5.257598992760788</v>
+        <v>5.264841203198588</v>
       </c>
       <c r="P10" t="n">
-        <v>401.1078836090256</v>
+        <v>401.1378364207976</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -33709,28 +33770,28 @@
         <v>0.1537</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.03391057229749807</v>
+        <v>-0.03782540652178903</v>
       </c>
       <c r="J11" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K11" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0009796170768284762</v>
+        <v>0.001219616061436279</v>
       </c>
       <c r="M11" t="n">
-        <v>6.403362989668109</v>
+        <v>6.414636485768544</v>
       </c>
       <c r="N11" t="n">
-        <v>67.52647108910325</v>
+        <v>67.61580629694666</v>
       </c>
       <c r="O11" t="n">
-        <v>8.217449183846728</v>
+        <v>8.222883089096346</v>
       </c>
       <c r="P11" t="n">
-        <v>392.3714676172999</v>
+        <v>392.4103895206991</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -33791,28 +33852,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0391534257939407</v>
+        <v>-0.04439521516188226</v>
       </c>
       <c r="J12" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K12" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L12" t="n">
-        <v>0.000671092317833355</v>
+        <v>0.0008636058209502417</v>
       </c>
       <c r="M12" t="n">
-        <v>9.343109407373742</v>
+        <v>9.351668294810883</v>
       </c>
       <c r="N12" t="n">
-        <v>131.4472581233384</v>
+        <v>131.5878229121345</v>
       </c>
       <c r="O12" t="n">
-        <v>11.46504505544302</v>
+        <v>11.47117356298537</v>
       </c>
       <c r="P12" t="n">
-        <v>390.6214246043228</v>
+        <v>390.6735393064351</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -33873,28 +33934,28 @@
         <v>0.0965</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1180129276704298</v>
+        <v>-0.1241709817590824</v>
       </c>
       <c r="J13" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K13" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004436578970243632</v>
+        <v>0.004914734660651066</v>
       </c>
       <c r="M13" t="n">
-        <v>11.12853424517228</v>
+        <v>11.13503596751503</v>
       </c>
       <c r="N13" t="n">
-        <v>179.2621115863057</v>
+        <v>179.4558381583032</v>
       </c>
       <c r="O13" t="n">
-        <v>13.38888014683475</v>
+        <v>13.39611280029782</v>
       </c>
       <c r="P13" t="n">
-        <v>396.9178918545134</v>
+        <v>396.9793454080516</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -33955,28 +34016,28 @@
         <v>0.1218</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1220464818740649</v>
+        <v>-0.1281437615621336</v>
       </c>
       <c r="J14" t="n">
+        <v>530</v>
+      </c>
+      <c r="K14" t="n">
         <v>529</v>
       </c>
-      <c r="K14" t="n">
-        <v>528</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.008799144018571736</v>
+        <v>0.009678684437474105</v>
       </c>
       <c r="M14" t="n">
-        <v>7.824681667375961</v>
+        <v>7.834500583737458</v>
       </c>
       <c r="N14" t="n">
-        <v>96.07472003829932</v>
+        <v>96.41466704942525</v>
       </c>
       <c r="O14" t="n">
-        <v>9.801771270454097</v>
+        <v>9.819097058763868</v>
       </c>
       <c r="P14" t="n">
-        <v>389.1292488856944</v>
+        <v>389.1901398892369</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -34018,7 +34079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O530"/>
+  <dimension ref="A1:O531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74811,6 +74872,83 @@
         </is>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>-35.00693565998607,173.77984592383993</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>-35.00673812042768,173.78062658740586</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>-35.00649468704829,173.7814199271811</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>-35.00621828523334,173.78225857877848</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>-35.00593141759077,173.78308306118262</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>-35.0056220083776,173.78388419564527</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>-35.00526829665742,173.78463663033352</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>-35.00486143350706,173.78535125739236</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>-35.004411284737365,173.7859917663345</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>-35.003918518256626,173.78662514091582</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>-35.00337432601749,173.78726299453123</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>-35.00292121677509,173.78798769286055</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>-35.00254998624372,173.78875685186952</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0045/nzd0045.xlsx
+++ b/data/nzd0045/nzd0045.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O531"/>
+  <dimension ref="A1:O533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27525,6 +27525,108 @@
       <c r="O531" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>401.11</v>
+      </c>
+      <c r="C532" t="n">
+        <v>409.16</v>
+      </c>
+      <c r="D532" t="n">
+        <v>399.2</v>
+      </c>
+      <c r="E532" t="n">
+        <v>396.59</v>
+      </c>
+      <c r="F532" t="n">
+        <v>393.25</v>
+      </c>
+      <c r="G532" t="n">
+        <v>394.17</v>
+      </c>
+      <c r="H532" t="n">
+        <v>394.51</v>
+      </c>
+      <c r="I532" t="n">
+        <v>394.16</v>
+      </c>
+      <c r="J532" t="n">
+        <v>395.72</v>
+      </c>
+      <c r="K532" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="L532" t="n">
+        <v>375.73</v>
+      </c>
+      <c r="M532" t="n">
+        <v>377.06</v>
+      </c>
+      <c r="N532" t="n">
+        <v>369.56</v>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>400.85</v>
+      </c>
+      <c r="C533" t="n">
+        <v>408.71</v>
+      </c>
+      <c r="D533" t="n">
+        <v>398.51</v>
+      </c>
+      <c r="E533" t="n">
+        <v>396.19</v>
+      </c>
+      <c r="F533" t="n">
+        <v>393.13</v>
+      </c>
+      <c r="G533" t="n">
+        <v>394.18</v>
+      </c>
+      <c r="H533" t="n">
+        <v>394.42</v>
+      </c>
+      <c r="I533" t="n">
+        <v>394.17</v>
+      </c>
+      <c r="J533" t="n">
+        <v>396.01</v>
+      </c>
+      <c r="K533" t="n">
+        <v>381.75</v>
+      </c>
+      <c r="L533" t="n">
+        <v>375.54</v>
+      </c>
+      <c r="M533" t="n">
+        <v>376.14</v>
+      </c>
+      <c r="N533" t="n">
+        <v>369.94</v>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -27539,7 +27641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B535"/>
+  <dimension ref="A1:B537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32892,6 +32994,26 @@
       </c>
       <c r="B535" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -33060,28 +33182,28 @@
         <v>0.1432</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1446018130926982</v>
+        <v>0.1435069550099035</v>
       </c>
       <c r="J2" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K2" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L2" t="n">
-        <v>0.053910136547902</v>
+        <v>0.05352974355912421</v>
       </c>
       <c r="M2" t="n">
-        <v>3.424113617190299</v>
+        <v>3.417216185312111</v>
       </c>
       <c r="N2" t="n">
-        <v>21.21374612830157</v>
+        <v>21.14244387253399</v>
       </c>
       <c r="O2" t="n">
-        <v>4.605838265538812</v>
+        <v>4.598091329294579</v>
       </c>
       <c r="P2" t="n">
-        <v>398.6877223410709</v>
+        <v>398.6986277889935</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33142,28 +33264,28 @@
         <v>0.1717</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1337543924201816</v>
+        <v>0.1327988304884927</v>
       </c>
       <c r="J3" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K3" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04944921410815128</v>
+        <v>0.04914211855330286</v>
       </c>
       <c r="M3" t="n">
-        <v>3.358594629453658</v>
+        <v>3.352141698770411</v>
       </c>
       <c r="N3" t="n">
-        <v>19.88107987391241</v>
+        <v>19.81288486292963</v>
       </c>
       <c r="O3" t="n">
-        <v>4.458820457689725</v>
+        <v>4.451166685592624</v>
       </c>
       <c r="P3" t="n">
-        <v>406.7371825994618</v>
+        <v>406.7467009691111</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33220,28 +33342,28 @@
         <v>0.1431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1349024006287672</v>
+        <v>0.1330758883008402</v>
       </c>
       <c r="J4" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K4" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08265326441199916</v>
+        <v>0.08105912806899929</v>
       </c>
       <c r="M4" t="n">
-        <v>2.495322696789808</v>
+        <v>2.496841864164095</v>
       </c>
       <c r="N4" t="n">
-        <v>11.65593237096508</v>
+        <v>11.63624800936793</v>
       </c>
       <c r="O4" t="n">
-        <v>3.414078553719155</v>
+        <v>3.411194513563823</v>
       </c>
       <c r="P4" t="n">
-        <v>397.8316493789605</v>
+        <v>397.8498564261636</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33298,28 +33420,28 @@
         <v>0.1071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1556170823663185</v>
+        <v>0.1517892346125134</v>
       </c>
       <c r="J5" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K5" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1366189384864199</v>
+        <v>0.1304352334211063</v>
       </c>
       <c r="M5" t="n">
-        <v>2.181514515957506</v>
+        <v>2.194110134189072</v>
       </c>
       <c r="N5" t="n">
-        <v>8.831618533940867</v>
+        <v>8.902613883590311</v>
       </c>
       <c r="O5" t="n">
-        <v>2.971803919161032</v>
+        <v>2.983724833759023</v>
       </c>
       <c r="P5" t="n">
-        <v>397.5872304899649</v>
+        <v>397.6253853198727</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33376,28 +33498,28 @@
         <v>0.1192</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1076205761402559</v>
+        <v>0.1027362366264303</v>
       </c>
       <c r="J6" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K6" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05044125859840631</v>
+        <v>0.04594049246729759</v>
       </c>
       <c r="M6" t="n">
-        <v>2.797133147940867</v>
+        <v>2.816926615561102</v>
       </c>
       <c r="N6" t="n">
-        <v>12.58231926130612</v>
+        <v>12.70444519669841</v>
       </c>
       <c r="O6" t="n">
-        <v>3.547156503638671</v>
+        <v>3.564329557812859</v>
       </c>
       <c r="P6" t="n">
-        <v>397.1101017089896</v>
+        <v>397.1587865971532</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33454,28 +33576,28 @@
         <v>0.1403</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1641055435332991</v>
+        <v>0.1576708336951191</v>
       </c>
       <c r="J7" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K7" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07943170113935161</v>
+        <v>0.0732218870021637</v>
       </c>
       <c r="M7" t="n">
-        <v>3.377637401409119</v>
+        <v>3.390831574631108</v>
       </c>
       <c r="N7" t="n">
-        <v>18.01120664609445</v>
+        <v>18.23753594850475</v>
       </c>
       <c r="O7" t="n">
-        <v>4.243961197524602</v>
+        <v>4.270542816610641</v>
       </c>
       <c r="P7" t="n">
-        <v>398.7569194716881</v>
+        <v>398.8210574581014</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33532,28 +33654,28 @@
         <v>0.1456</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1222524925920776</v>
+        <v>0.1165269822489498</v>
       </c>
       <c r="J8" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K8" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03570707133963069</v>
+        <v>0.03248879192426313</v>
       </c>
       <c r="M8" t="n">
-        <v>3.679231018205187</v>
+        <v>3.689666847177162</v>
       </c>
       <c r="N8" t="n">
-        <v>23.29186958449125</v>
+        <v>23.43710804363548</v>
       </c>
       <c r="O8" t="n">
-        <v>4.826165101246667</v>
+        <v>4.841188701510765</v>
       </c>
       <c r="P8" t="n">
-        <v>399.1649652267697</v>
+        <v>399.2220344427236</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33610,28 +33732,28 @@
         <v>0.1405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09634460352240237</v>
+        <v>0.09120518423958196</v>
       </c>
       <c r="J9" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K9" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01859063833938213</v>
+        <v>0.01671687262237775</v>
       </c>
       <c r="M9" t="n">
-        <v>3.981499999811406</v>
+        <v>3.9910632508438</v>
       </c>
       <c r="N9" t="n">
-        <v>28.27774901776437</v>
+        <v>28.35901776518279</v>
       </c>
       <c r="O9" t="n">
-        <v>5.317682673661937</v>
+        <v>5.32531855997205</v>
       </c>
       <c r="P9" t="n">
-        <v>398.738699176091</v>
+        <v>398.789926351273</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33688,28 +33810,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05828812031309059</v>
+        <v>0.05336608722931879</v>
       </c>
       <c r="J10" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K10" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00702364589030724</v>
+        <v>0.005905457192375008</v>
       </c>
       <c r="M10" t="n">
-        <v>4.18225241108039</v>
+        <v>4.194246834503585</v>
       </c>
       <c r="N10" t="n">
-        <v>27.71855289489756</v>
+        <v>27.78647582795007</v>
       </c>
       <c r="O10" t="n">
-        <v>5.264841203198588</v>
+        <v>5.271287871853525</v>
       </c>
       <c r="P10" t="n">
-        <v>401.1378364207976</v>
+        <v>401.1868962785663</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -33770,28 +33892,28 @@
         <v>0.1537</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.03782540652178903</v>
+        <v>-0.04470220700593996</v>
       </c>
       <c r="J11" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K11" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001219616061436279</v>
+        <v>0.001707934947254075</v>
       </c>
       <c r="M11" t="n">
-        <v>6.414636485768544</v>
+        <v>6.431203029515413</v>
       </c>
       <c r="N11" t="n">
-        <v>67.61580629694666</v>
+        <v>67.69752726164091</v>
       </c>
       <c r="O11" t="n">
-        <v>8.222883089096346</v>
+        <v>8.227850707301446</v>
       </c>
       <c r="P11" t="n">
-        <v>392.4103895206991</v>
+        <v>392.4789346487212</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -33852,28 +33974,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.04439521516188226</v>
+        <v>-0.05442551838268841</v>
       </c>
       <c r="J12" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K12" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0008636058209502417</v>
+        <v>0.001300852046023926</v>
       </c>
       <c r="M12" t="n">
-        <v>9.351668294810883</v>
+        <v>9.36633268380416</v>
       </c>
       <c r="N12" t="n">
-        <v>131.5878229121345</v>
+        <v>131.8076158296068</v>
       </c>
       <c r="O12" t="n">
-        <v>11.47117356298537</v>
+        <v>11.480749793877</v>
       </c>
       <c r="P12" t="n">
-        <v>390.6735393064351</v>
+        <v>390.773516758218</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -33934,28 +34056,28 @@
         <v>0.0965</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1241709817590824</v>
+        <v>-0.136605203597646</v>
       </c>
       <c r="J13" t="n">
+        <v>532</v>
+      </c>
+      <c r="K13" t="n">
         <v>530</v>
       </c>
-      <c r="K13" t="n">
-        <v>528</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.004914734660651066</v>
+        <v>0.005954309505936339</v>
       </c>
       <c r="M13" t="n">
-        <v>11.13503596751503</v>
+        <v>11.14818128860526</v>
       </c>
       <c r="N13" t="n">
-        <v>179.4558381583032</v>
+        <v>179.8710876531218</v>
       </c>
       <c r="O13" t="n">
-        <v>13.39611280029782</v>
+        <v>13.41160272499606</v>
       </c>
       <c r="P13" t="n">
-        <v>396.9793454080516</v>
+        <v>397.1037486945872</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -34016,28 +34138,28 @@
         <v>0.1218</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1281437615621336</v>
+        <v>-0.1398213710310351</v>
       </c>
       <c r="J14" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K14" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L14" t="n">
-        <v>0.009678684437474105</v>
+        <v>0.01148135322848287</v>
       </c>
       <c r="M14" t="n">
-        <v>7.834500583737458</v>
+        <v>7.852352568271838</v>
       </c>
       <c r="N14" t="n">
-        <v>96.41466704942525</v>
+        <v>97.01235705023994</v>
       </c>
       <c r="O14" t="n">
-        <v>9.819097058763868</v>
+        <v>9.84948511599667</v>
       </c>
       <c r="P14" t="n">
-        <v>389.1901398892369</v>
+        <v>389.3070544482593</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -34079,7 +34201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O531"/>
+  <dimension ref="A1:O533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74949,6 +75071,160 @@
         </is>
       </c>
     </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>-35.00692249272417,173.77984267941926</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>-35.00672801059322,173.78062221783233</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>-35.00649062594546,173.7814175475828</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>-35.006215588480856,173.78225705034606</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-35.0059243360231,173.78307895937724</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>-35.00561593541706,173.78388033693918</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>-35.005259367313634,173.78462959864325</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>-35.00485188664072,173.78534225669065</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>-35.0044034557613,173.78598160950713</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>-35.003911074239014,173.78661357439282</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>-35.003370846726476,173.787259013001</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>-35.00292070813696,173.78798723865515</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>-35.002547806300264,173.7887549053928</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>-35.00692479036721,173.7798432455597</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>-35.00673183363989,173.78062387019193</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>-35.006496230267345,173.7814208314285</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>-35.00621885727175,173.78225890299146</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>-35.005925312791064,173.78307952514345</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>-35.005615855509696,173.78388028616675</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>-35.0052600483653,173.78463013495855</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>-35.00485181539545,173.78534218952123</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>-35.004401668042235,173.7859792902319</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>-35.00391285191496,173.78661633654738</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>-35.0033720940195,173.787260440342</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>-35.00292739309524,173.78799320821255</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>-35.00254504503852,173.78875243985578</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0045/nzd0045.xlsx
+++ b/data/nzd0045/nzd0045.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O533"/>
+  <dimension ref="A1:O536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27625,6 +27625,159 @@
         <v>369.94</v>
       </c>
       <c r="O533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>398.72</v>
+      </c>
+      <c r="C534" t="n">
+        <v>406.92</v>
+      </c>
+      <c r="D534" t="n">
+        <v>396.81</v>
+      </c>
+      <c r="E534" t="n">
+        <v>394.11</v>
+      </c>
+      <c r="F534" t="n">
+        <v>391.97</v>
+      </c>
+      <c r="G534" t="n">
+        <v>392.83</v>
+      </c>
+      <c r="H534" t="n">
+        <v>393.47</v>
+      </c>
+      <c r="I534" t="n">
+        <v>393.51</v>
+      </c>
+      <c r="J534" t="n">
+        <v>395.13</v>
+      </c>
+      <c r="K534" t="n">
+        <v>381.54</v>
+      </c>
+      <c r="L534" t="n">
+        <v>374.43</v>
+      </c>
+      <c r="M534" t="n">
+        <v>373.76</v>
+      </c>
+      <c r="N534" t="n">
+        <v>368.29</v>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>398.72</v>
+      </c>
+      <c r="C535" t="n">
+        <v>406.92</v>
+      </c>
+      <c r="D535" t="n">
+        <v>396.81</v>
+      </c>
+      <c r="E535" t="n">
+        <v>394.07</v>
+      </c>
+      <c r="F535" t="n">
+        <v>391.82</v>
+      </c>
+      <c r="G535" t="n">
+        <v>392.79</v>
+      </c>
+      <c r="H535" t="n">
+        <v>393.3</v>
+      </c>
+      <c r="I535" t="n">
+        <v>393.4</v>
+      </c>
+      <c r="J535" t="n">
+        <v>395</v>
+      </c>
+      <c r="K535" t="n">
+        <v>381.54</v>
+      </c>
+      <c r="L535" t="n">
+        <v>374.43</v>
+      </c>
+      <c r="M535" t="n">
+        <v>373.76</v>
+      </c>
+      <c r="N535" t="n">
+        <v>368.29</v>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="C536" t="n">
+        <v>407.72</v>
+      </c>
+      <c r="D536" t="n">
+        <v>397.8</v>
+      </c>
+      <c r="E536" t="n">
+        <v>394.7</v>
+      </c>
+      <c r="F536" t="n">
+        <v>392.34</v>
+      </c>
+      <c r="G536" t="n">
+        <v>393.52</v>
+      </c>
+      <c r="H536" t="n">
+        <v>393.93</v>
+      </c>
+      <c r="I536" t="n">
+        <v>393.89</v>
+      </c>
+      <c r="J536" t="n">
+        <v>395.29</v>
+      </c>
+      <c r="K536" t="n">
+        <v>381.79</v>
+      </c>
+      <c r="L536" t="n">
+        <v>374.88</v>
+      </c>
+      <c r="M536" t="n">
+        <v>374.26</v>
+      </c>
+      <c r="N536" t="n">
+        <v>369.07</v>
+      </c>
+      <c r="O536" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27641,7 +27794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B537"/>
+  <dimension ref="A1:B540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33014,6 +33167,36 @@
       </c>
       <c r="B537" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -33182,28 +33365,28 @@
         <v>0.1432</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1435069550099035</v>
+        <v>0.1396776319103638</v>
       </c>
       <c r="J2" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K2" t="n">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05352974355912421</v>
+        <v>0.05127710807909347</v>
       </c>
       <c r="M2" t="n">
-        <v>3.417216185312111</v>
+        <v>3.418796540360636</v>
       </c>
       <c r="N2" t="n">
-        <v>21.14244387253399</v>
+        <v>21.09455092639135</v>
       </c>
       <c r="O2" t="n">
-        <v>4.598091329294579</v>
+        <v>4.59288046071214</v>
       </c>
       <c r="P2" t="n">
-        <v>398.6986277889935</v>
+        <v>398.7368805683278</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33264,28 +33447,28 @@
         <v>0.1717</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1327988304884927</v>
+        <v>0.1295149142848492</v>
       </c>
       <c r="J3" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K3" t="n">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04914211855330286</v>
+        <v>0.04727671570482395</v>
       </c>
       <c r="M3" t="n">
-        <v>3.352141698770411</v>
+        <v>3.354401063961024</v>
       </c>
       <c r="N3" t="n">
-        <v>19.81288486292963</v>
+        <v>19.75421367806027</v>
       </c>
       <c r="O3" t="n">
-        <v>4.451166685592624</v>
+        <v>4.44457125919478</v>
       </c>
       <c r="P3" t="n">
-        <v>406.7467009691111</v>
+        <v>406.7795046337437</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33342,28 +33525,28 @@
         <v>0.1431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1330758883008402</v>
+        <v>0.1285503267854581</v>
       </c>
       <c r="J4" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K4" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08105912806899929</v>
+        <v>0.07630079789529798</v>
       </c>
       <c r="M4" t="n">
-        <v>2.496841864164095</v>
+        <v>2.510202016608893</v>
       </c>
       <c r="N4" t="n">
-        <v>11.63624800936793</v>
+        <v>11.67043285796926</v>
       </c>
       <c r="O4" t="n">
-        <v>3.411194513563823</v>
+        <v>3.41620152478879</v>
       </c>
       <c r="P4" t="n">
-        <v>397.8498564261636</v>
+        <v>397.8950963964365</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33420,28 +33603,28 @@
         <v>0.1071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1517892346125134</v>
+        <v>0.1439250537394975</v>
       </c>
       <c r="J5" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K5" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1304352334211063</v>
+        <v>0.1166628731806385</v>
       </c>
       <c r="M5" t="n">
-        <v>2.194110134189072</v>
+        <v>2.225522781228409</v>
       </c>
       <c r="N5" t="n">
-        <v>8.902613883590311</v>
+        <v>9.14967614189602</v>
       </c>
       <c r="O5" t="n">
-        <v>2.983724833759023</v>
+        <v>3.024843159883834</v>
       </c>
       <c r="P5" t="n">
-        <v>397.6253853198727</v>
+        <v>397.7040028483501</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33498,28 +33681,28 @@
         <v>0.1192</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1027362366264303</v>
+        <v>0.09435101886146965</v>
       </c>
       <c r="J6" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K6" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04594049246729759</v>
+        <v>0.03849672801827853</v>
       </c>
       <c r="M6" t="n">
-        <v>2.816926615561102</v>
+        <v>2.853405903049181</v>
       </c>
       <c r="N6" t="n">
-        <v>12.70444519669841</v>
+        <v>12.97057537315262</v>
       </c>
       <c r="O6" t="n">
-        <v>3.564329557812859</v>
+        <v>3.601468502312997</v>
       </c>
       <c r="P6" t="n">
-        <v>397.1587865971532</v>
+        <v>397.2426134470828</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33576,28 +33759,28 @@
         <v>0.1403</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1576708336951191</v>
+        <v>0.1470244942159314</v>
       </c>
       <c r="J7" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K7" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0732218870021637</v>
+        <v>0.06323916021703391</v>
       </c>
       <c r="M7" t="n">
-        <v>3.390831574631108</v>
+        <v>3.41687614750005</v>
       </c>
       <c r="N7" t="n">
-        <v>18.23753594850475</v>
+        <v>18.67932277439725</v>
       </c>
       <c r="O7" t="n">
-        <v>4.270542816610641</v>
+        <v>4.321958210625972</v>
       </c>
       <c r="P7" t="n">
-        <v>398.8210574581014</v>
+        <v>398.9274882871405</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33654,28 +33837,28 @@
         <v>0.1456</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1165269822489498</v>
+        <v>0.1071704371303943</v>
       </c>
       <c r="J8" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K8" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03248879192426313</v>
+        <v>0.02746461662996325</v>
       </c>
       <c r="M8" t="n">
-        <v>3.689666847177162</v>
+        <v>3.708321386548512</v>
       </c>
       <c r="N8" t="n">
-        <v>23.43710804363548</v>
+        <v>23.72580624871411</v>
       </c>
       <c r="O8" t="n">
-        <v>4.841188701510765</v>
+        <v>4.870914313423519</v>
       </c>
       <c r="P8" t="n">
-        <v>399.2220344427236</v>
+        <v>399.3155715154963</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33732,28 +33915,28 @@
         <v>0.1405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09120518423958196</v>
+        <v>0.08306314741669096</v>
       </c>
       <c r="J9" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K9" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01671687262237775</v>
+        <v>0.01391710993668138</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9910632508438</v>
+        <v>4.00767128620835</v>
       </c>
       <c r="N9" t="n">
-        <v>28.35901776518279</v>
+        <v>28.5180770048772</v>
       </c>
       <c r="O9" t="n">
-        <v>5.32531855997205</v>
+        <v>5.340231924259208</v>
       </c>
       <c r="P9" t="n">
-        <v>398.789926351273</v>
+        <v>398.8713221032457</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33810,28 +33993,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05336608722931879</v>
+        <v>0.04537343042806589</v>
       </c>
       <c r="J10" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K10" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005905457192375008</v>
+        <v>0.004280547794382028</v>
       </c>
       <c r="M10" t="n">
-        <v>4.194246834503585</v>
+        <v>4.215215637228197</v>
       </c>
       <c r="N10" t="n">
-        <v>27.78647582795007</v>
+        <v>27.93701342657427</v>
       </c>
       <c r="O10" t="n">
-        <v>5.271287871853525</v>
+        <v>5.285547599499438</v>
       </c>
       <c r="P10" t="n">
-        <v>401.1868962785663</v>
+        <v>401.2667992246357</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -33892,28 +34075,28 @@
         <v>0.1537</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.04470220700593996</v>
+        <v>-0.05507257702228455</v>
       </c>
       <c r="J11" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K11" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001707934947254075</v>
+        <v>0.00260155946566587</v>
       </c>
       <c r="M11" t="n">
-        <v>6.431203029515413</v>
+        <v>6.455815082424325</v>
       </c>
       <c r="N11" t="n">
-        <v>67.69752726164091</v>
+        <v>67.83359450001569</v>
       </c>
       <c r="O11" t="n">
-        <v>8.227850707301446</v>
+        <v>8.236115255386832</v>
       </c>
       <c r="P11" t="n">
-        <v>392.4789346487212</v>
+        <v>392.5826077522379</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -33974,28 +34157,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.05442551838268841</v>
+        <v>-0.07024319201890639</v>
       </c>
       <c r="J12" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K12" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001300852046023926</v>
+        <v>0.002171439636928896</v>
       </c>
       <c r="M12" t="n">
-        <v>9.36633268380416</v>
+        <v>9.391944661422425</v>
       </c>
       <c r="N12" t="n">
-        <v>131.8076158296068</v>
+        <v>132.2682940455039</v>
       </c>
       <c r="O12" t="n">
-        <v>11.480749793877</v>
+        <v>11.50079536577814</v>
       </c>
       <c r="P12" t="n">
-        <v>390.773516758218</v>
+        <v>390.9316466506543</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -34056,28 +34239,28 @@
         <v>0.0965</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.136605203597646</v>
+        <v>-0.1576818505367305</v>
       </c>
       <c r="J13" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K13" t="n">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005954309505936339</v>
+        <v>0.007920458345998083</v>
       </c>
       <c r="M13" t="n">
-        <v>11.14818128860526</v>
+        <v>11.17829856862383</v>
       </c>
       <c r="N13" t="n">
-        <v>179.8710876531218</v>
+        <v>180.9766302320499</v>
       </c>
       <c r="O13" t="n">
-        <v>13.41160272499606</v>
+        <v>13.45275548845105</v>
       </c>
       <c r="P13" t="n">
-        <v>397.1037486945872</v>
+        <v>397.3152396906073</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -34138,28 +34321,28 @@
         <v>0.1218</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1398213710310351</v>
+        <v>-0.1582044075058789</v>
       </c>
       <c r="J14" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K14" t="n">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01148135322848287</v>
+        <v>0.01458818826034203</v>
       </c>
       <c r="M14" t="n">
-        <v>7.852352568271838</v>
+        <v>7.882730953849175</v>
       </c>
       <c r="N14" t="n">
-        <v>97.01235705023994</v>
+        <v>98.07541434278019</v>
       </c>
       <c r="O14" t="n">
-        <v>9.84948511599667</v>
+        <v>9.903303203617478</v>
       </c>
       <c r="P14" t="n">
-        <v>389.3070544482593</v>
+        <v>389.4916458681047</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -34201,7 +34384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O533"/>
+  <dimension ref="A1:O536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75225,6 +75408,237 @@
         </is>
       </c>
     </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>-35.006943613365685,173.7798478835576</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>-35.0067470408697,173.78063044291284</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>-35.00651003801647,173.78142892206478</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>-35.006235854983885,173.7822685367499</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>-35.005934754881245,173.78308499421763</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>-35.00562664300529,173.7838871404477</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>-35.00526723724377,173.7846357960651</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>-35.00485651758345,173.7853466227024</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>-35.004407092844765,173.78598632803298</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>-35.00391401851477,173.78661814921136</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>-35.003379380836265,173.7872687790191</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>-35.002944686790194,173.78800865120257</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>-35.002557034727275,173.7887631454783</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>-35.006943613365685,173.7798478835576</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>-35.0067470408697,173.78063044291284</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>-35.00651003801647,173.78142892206478</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>-35.00623618186297,173.78226872201455</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>-35.00593597584116,173.7830857014256</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>-35.005626962634786,173.78388734353754</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>-35.00526852367464,173.7846368091053</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>-35.00485730128143,173.78534736156598</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>-35.00440789423603,173.78598736770823</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>-35.00391401851477,173.78661814921136</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>-35.003379380836265,173.7872687790191</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>-35.002944686790194,173.78800865120257</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>-35.002557034727275,173.7887631454783</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>-35.00693848785439,173.77984662062838</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>-35.00674024434247,173.78062750538365</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>-35.006501997033226,173.78142421045862</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>-35.00623103351755,173.78226580409688</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>-35.0059317431801,173.7830832497714</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>-35.00562112939647,173.7838836371483</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>-35.00526375631317,173.7846330548976</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>-35.0048538102631,173.7853440702647</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>-35.004406106517074,173.78598504843274</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>-35.00391262970547,173.78661599127807</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>-35.00337642672144,173.78726539847415</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>-35.00294105366118,173.7880054068764</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>-35.002551366874535,173.78875808463818</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0045/nzd0045.xlsx
+++ b/data/nzd0045/nzd0045.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O536"/>
+  <dimension ref="A1:O537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27780,6 +27780,57 @@
       <c r="O536" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>397.96</v>
+      </c>
+      <c r="C537" t="n">
+        <v>407.28</v>
+      </c>
+      <c r="D537" t="n">
+        <v>398.04</v>
+      </c>
+      <c r="E537" t="n">
+        <v>394.73</v>
+      </c>
+      <c r="F537" t="n">
+        <v>393.25</v>
+      </c>
+      <c r="G537" t="n">
+        <v>393.5</v>
+      </c>
+      <c r="H537" t="n">
+        <v>394.42</v>
+      </c>
+      <c r="I537" t="n">
+        <v>393.94</v>
+      </c>
+      <c r="J537" t="n">
+        <v>395.12</v>
+      </c>
+      <c r="K537" t="n">
+        <v>382.52</v>
+      </c>
+      <c r="L537" t="n">
+        <v>373.76</v>
+      </c>
+      <c r="M537" t="n">
+        <v>373.21</v>
+      </c>
+      <c r="N537" t="n">
+        <v>370.57</v>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -27794,7 +27845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B540"/>
+  <dimension ref="A1:B541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33197,6 +33248,16 @@
       </c>
       <c r="B540" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -33365,28 +33426,28 @@
         <v>0.1432</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1396776319103638</v>
+        <v>0.1380659957671896</v>
       </c>
       <c r="J2" t="n">
+        <v>536</v>
+      </c>
+      <c r="K2" t="n">
         <v>535</v>
       </c>
-      <c r="K2" t="n">
-        <v>534</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.05127710807909347</v>
+        <v>0.05026937729014658</v>
       </c>
       <c r="M2" t="n">
-        <v>3.418796540360636</v>
+        <v>3.421025568004312</v>
       </c>
       <c r="N2" t="n">
-        <v>21.09455092639135</v>
+        <v>21.09241761458336</v>
       </c>
       <c r="O2" t="n">
-        <v>4.59288046071214</v>
+        <v>4.592648213676219</v>
       </c>
       <c r="P2" t="n">
-        <v>398.7368805683278</v>
+        <v>398.7530884084377</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33447,28 +33508,28 @@
         <v>0.1717</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1295149142848492</v>
+        <v>0.128460694244753</v>
       </c>
       <c r="J3" t="n">
+        <v>536</v>
+      </c>
+      <c r="K3" t="n">
         <v>535</v>
       </c>
-      <c r="K3" t="n">
-        <v>534</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.04727671570482395</v>
+        <v>0.04669083949065467</v>
       </c>
       <c r="M3" t="n">
-        <v>3.354401063961024</v>
+        <v>3.354818808440445</v>
       </c>
       <c r="N3" t="n">
-        <v>19.75421367806027</v>
+        <v>19.73324826269697</v>
       </c>
       <c r="O3" t="n">
-        <v>4.44457125919478</v>
+        <v>4.44221209114299</v>
       </c>
       <c r="P3" t="n">
-        <v>406.7795046337437</v>
+        <v>406.7901066731202</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33525,28 +33586,28 @@
         <v>0.1431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1285503267854581</v>
+        <v>0.1273768595451887</v>
       </c>
       <c r="J4" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K4" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07630079789529798</v>
+        <v>0.07518350988780564</v>
       </c>
       <c r="M4" t="n">
-        <v>2.510202016608893</v>
+        <v>2.5126295095706</v>
       </c>
       <c r="N4" t="n">
-        <v>11.67043285796926</v>
+        <v>11.6683876300915</v>
       </c>
       <c r="O4" t="n">
-        <v>3.41620152478879</v>
+        <v>3.415902169279955</v>
       </c>
       <c r="P4" t="n">
-        <v>397.8950963964365</v>
+        <v>397.9069060371181</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33603,28 +33664,28 @@
         <v>0.1071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1439250537394975</v>
+        <v>0.1414801035420645</v>
       </c>
       <c r="J5" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K5" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1166628731806385</v>
+        <v>0.1126506857122586</v>
       </c>
       <c r="M5" t="n">
-        <v>2.225522781228409</v>
+        <v>2.235218169518155</v>
       </c>
       <c r="N5" t="n">
-        <v>9.14967614189602</v>
+        <v>9.218246597022119</v>
       </c>
       <c r="O5" t="n">
-        <v>3.024843159883834</v>
+        <v>3.036156550150555</v>
       </c>
       <c r="P5" t="n">
-        <v>397.7040028483501</v>
+        <v>397.728608548727</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33681,28 +33742,28 @@
         <v>0.1192</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09435101886146965</v>
+        <v>0.0920135484767934</v>
       </c>
       <c r="J6" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K6" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03849672801827853</v>
+        <v>0.03661297237281913</v>
       </c>
       <c r="M6" t="n">
-        <v>2.853405903049181</v>
+        <v>2.862487655462854</v>
       </c>
       <c r="N6" t="n">
-        <v>12.97057537315262</v>
+        <v>13.02465326293287</v>
       </c>
       <c r="O6" t="n">
-        <v>3.601468502312997</v>
+        <v>3.608968448592045</v>
       </c>
       <c r="P6" t="n">
-        <v>397.2426134470828</v>
+        <v>397.2661374828631</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33759,28 +33820,28 @@
         <v>0.1403</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1470244942159314</v>
+        <v>0.1436693630505506</v>
       </c>
       <c r="J7" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K7" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06323916021703391</v>
+        <v>0.06030084799834001</v>
       </c>
       <c r="M7" t="n">
-        <v>3.41687614750005</v>
+        <v>3.42507399659542</v>
       </c>
       <c r="N7" t="n">
-        <v>18.67932277439725</v>
+        <v>18.80574545648377</v>
       </c>
       <c r="O7" t="n">
-        <v>4.321958210625972</v>
+        <v>4.336559172487304</v>
       </c>
       <c r="P7" t="n">
-        <v>398.9274882871405</v>
+        <v>398.9612539451352</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33837,28 +33898,28 @@
         <v>0.1456</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1071704371303943</v>
+        <v>0.1043852307788729</v>
       </c>
       <c r="J8" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K8" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02746461662996325</v>
+        <v>0.02607691747413199</v>
       </c>
       <c r="M8" t="n">
-        <v>3.708321386548512</v>
+        <v>3.713003840662262</v>
       </c>
       <c r="N8" t="n">
-        <v>23.72580624871411</v>
+        <v>23.79267778762085</v>
       </c>
       <c r="O8" t="n">
-        <v>4.870914313423519</v>
+        <v>4.877773855727717</v>
       </c>
       <c r="P8" t="n">
-        <v>399.3155715154963</v>
+        <v>399.3436015150625</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33915,28 +33976,28 @@
         <v>0.1405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08306314741669096</v>
+        <v>0.08049745571081129</v>
       </c>
       <c r="J9" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K9" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01391710993668138</v>
+        <v>0.01309158513014297</v>
       </c>
       <c r="M9" t="n">
-        <v>4.00767128620835</v>
+        <v>4.012596451159832</v>
       </c>
       <c r="N9" t="n">
-        <v>28.5180770048772</v>
+        <v>28.55917981436506</v>
       </c>
       <c r="O9" t="n">
-        <v>5.340231924259208</v>
+        <v>5.344078949114156</v>
       </c>
       <c r="P9" t="n">
-        <v>398.8713221032457</v>
+        <v>398.8971429324146</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33993,28 +34054,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04537343042806589</v>
+        <v>0.04272778736935113</v>
       </c>
       <c r="J10" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K10" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004280547794382028</v>
+        <v>0.003799586961604984</v>
       </c>
       <c r="M10" t="n">
-        <v>4.215215637228197</v>
+        <v>4.221891654910455</v>
       </c>
       <c r="N10" t="n">
-        <v>27.93701342657427</v>
+        <v>27.98516949709461</v>
       </c>
       <c r="O10" t="n">
-        <v>5.285547599499438</v>
+        <v>5.290101085716095</v>
       </c>
       <c r="P10" t="n">
-        <v>401.2667992246357</v>
+        <v>401.2934246751154</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -34075,28 +34136,28 @@
         <v>0.1537</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.05507257702228455</v>
+        <v>-0.05816694201046513</v>
       </c>
       <c r="J11" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K11" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00260155946566587</v>
+        <v>0.002907180683864086</v>
       </c>
       <c r="M11" t="n">
-        <v>6.455815082424325</v>
+        <v>6.461618336550289</v>
       </c>
       <c r="N11" t="n">
-        <v>67.83359450001569</v>
+        <v>67.84421697681422</v>
       </c>
       <c r="O11" t="n">
-        <v>8.236115255386832</v>
+        <v>8.236760101934147</v>
       </c>
       <c r="P11" t="n">
-        <v>392.5826077522379</v>
+        <v>392.6137490891191</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -34157,28 +34218,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.07024319201890639</v>
+        <v>-0.07575003568281688</v>
       </c>
       <c r="J12" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K12" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002171439636928896</v>
+        <v>0.002526343211242676</v>
       </c>
       <c r="M12" t="n">
-        <v>9.391944661422425</v>
+        <v>9.401300224302052</v>
       </c>
       <c r="N12" t="n">
-        <v>132.2682940455039</v>
+        <v>132.4559809450228</v>
       </c>
       <c r="O12" t="n">
-        <v>11.50079536577814</v>
+        <v>11.50895220882522</v>
       </c>
       <c r="P12" t="n">
-        <v>390.9316466506543</v>
+        <v>390.9870668982156</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -34239,28 +34300,28 @@
         <v>0.0965</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1576818505367305</v>
+        <v>-0.1648850904742679</v>
       </c>
       <c r="J13" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K13" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L13" t="n">
-        <v>0.007920458345998083</v>
+        <v>0.00865420124250027</v>
       </c>
       <c r="M13" t="n">
-        <v>11.17829856862383</v>
+        <v>11.18914259794253</v>
       </c>
       <c r="N13" t="n">
-        <v>180.9766302320499</v>
+        <v>181.3768330373213</v>
       </c>
       <c r="O13" t="n">
-        <v>13.45275548845105</v>
+        <v>13.46762165481795</v>
       </c>
       <c r="P13" t="n">
-        <v>397.3152396906073</v>
+        <v>397.3880020599695</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -34321,28 +34382,28 @@
         <v>0.1218</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1582044075058789</v>
+        <v>-0.1635284683101995</v>
       </c>
       <c r="J14" t="n">
+        <v>536</v>
+      </c>
+      <c r="K14" t="n">
         <v>535</v>
       </c>
-      <c r="K14" t="n">
-        <v>534</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.01458818826034203</v>
+        <v>0.01557066328706724</v>
       </c>
       <c r="M14" t="n">
-        <v>7.882730953849175</v>
+        <v>7.889709251929806</v>
       </c>
       <c r="N14" t="n">
-        <v>98.07541434278019</v>
+        <v>98.29495072001349</v>
       </c>
       <c r="O14" t="n">
-        <v>9.903303203617478</v>
+        <v>9.914381005388762</v>
       </c>
       <c r="P14" t="n">
-        <v>389.4916458681047</v>
+        <v>389.5454628092884</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -34384,7 +34445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O536"/>
+  <dimension ref="A1:O537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75639,6 +75700,83 @@
         </is>
       </c>
     </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>-35.00695032955288,173.77984953843065</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>-35.00674398243246,173.78062912102465</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>-35.00650004770392,173.7814230682512</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>-35.006230788358245,173.7822656651484</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>-35.0059243360231,173.78307895937724</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>-35.00562128921123,173.78388373869322</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>-35.0052600483653,173.78463013495855</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>-35.00485345403674,173.78534373441764</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>-35.00440715449025,173.785986408008</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>-35.003908574382095,173.7866096901132</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>-35.00338377918484,173.78727381227534</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>-35.00294868323201,173.78801221996173</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>-35.00254046715709,173.7887483522553</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0045/nzd0045.xlsx
+++ b/data/nzd0045/nzd0045.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O537"/>
+  <dimension ref="A1:O540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27831,6 +27831,159 @@
       <c r="O537" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>398.97</v>
+      </c>
+      <c r="C538" t="n">
+        <v>407.64</v>
+      </c>
+      <c r="D538" t="n">
+        <v>398.29</v>
+      </c>
+      <c r="E538" t="n">
+        <v>395.22</v>
+      </c>
+      <c r="F538" t="n">
+        <v>393.88</v>
+      </c>
+      <c r="G538" t="n">
+        <v>393.78</v>
+      </c>
+      <c r="H538" t="n">
+        <v>394.55</v>
+      </c>
+      <c r="I538" t="n">
+        <v>394.04</v>
+      </c>
+      <c r="J538" t="n">
+        <v>394.43</v>
+      </c>
+      <c r="K538" t="n">
+        <v>382.08</v>
+      </c>
+      <c r="L538" t="n">
+        <v>373.46</v>
+      </c>
+      <c r="M538" t="n">
+        <v>373.65</v>
+      </c>
+      <c r="N538" t="n">
+        <v>372.16</v>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>400.06</v>
+      </c>
+      <c r="C539" t="n">
+        <v>407.5</v>
+      </c>
+      <c r="D539" t="n">
+        <v>397.88</v>
+      </c>
+      <c r="E539" t="n">
+        <v>395.05</v>
+      </c>
+      <c r="F539" t="n">
+        <v>393.2</v>
+      </c>
+      <c r="G539" t="n">
+        <v>393.85</v>
+      </c>
+      <c r="H539" t="n">
+        <v>394.55</v>
+      </c>
+      <c r="I539" t="n">
+        <v>394.3</v>
+      </c>
+      <c r="J539" t="n">
+        <v>393.94</v>
+      </c>
+      <c r="K539" t="n">
+        <v>381.63</v>
+      </c>
+      <c r="L539" t="n">
+        <v>372.87</v>
+      </c>
+      <c r="M539" t="n">
+        <v>373.91</v>
+      </c>
+      <c r="N539" t="n">
+        <v>373.98</v>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>400.78</v>
+      </c>
+      <c r="C540" t="n">
+        <v>408.11</v>
+      </c>
+      <c r="D540" t="n">
+        <v>398.29</v>
+      </c>
+      <c r="E540" t="n">
+        <v>395.59</v>
+      </c>
+      <c r="F540" t="n">
+        <v>392.9</v>
+      </c>
+      <c r="G540" t="n">
+        <v>393.02</v>
+      </c>
+      <c r="H540" t="n">
+        <v>394.12</v>
+      </c>
+      <c r="I540" t="n">
+        <v>394.04</v>
+      </c>
+      <c r="J540" t="n">
+        <v>393.31</v>
+      </c>
+      <c r="K540" t="n">
+        <v>380.88</v>
+      </c>
+      <c r="L540" t="n">
+        <v>372.34</v>
+      </c>
+      <c r="M540" t="n">
+        <v>373.39</v>
+      </c>
+      <c r="N540" t="n">
+        <v>373.79</v>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -27845,7 +27998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B541"/>
+  <dimension ref="A1:B544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33258,6 +33411,36 @@
       </c>
       <c r="B541" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -33426,28 +33609,28 @@
         <v>0.1432</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1380659957671896</v>
+        <v>0.1353961822308057</v>
       </c>
       <c r="J2" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K2" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05026937729014658</v>
+        <v>0.0489246743494417</v>
       </c>
       <c r="M2" t="n">
-        <v>3.421025568004312</v>
+        <v>3.416280224128933</v>
       </c>
       <c r="N2" t="n">
-        <v>21.09241761458336</v>
+        <v>21.01187502696801</v>
       </c>
       <c r="O2" t="n">
-        <v>4.592648213676219</v>
+        <v>4.583871183505052</v>
       </c>
       <c r="P2" t="n">
-        <v>398.7530884084377</v>
+        <v>398.7800803269538</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33508,28 +33691,28 @@
         <v>0.1717</v>
       </c>
       <c r="I3" t="n">
-        <v>0.128460694244753</v>
+        <v>0.1258218625197281</v>
       </c>
       <c r="J3" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K3" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04669083949065467</v>
+        <v>0.04533320240231387</v>
       </c>
       <c r="M3" t="n">
-        <v>3.354818808440445</v>
+        <v>3.352713591817678</v>
       </c>
       <c r="N3" t="n">
-        <v>19.73324826269697</v>
+        <v>19.65679186276278</v>
       </c>
       <c r="O3" t="n">
-        <v>4.44221209114299</v>
+        <v>4.433598071855723</v>
       </c>
       <c r="P3" t="n">
-        <v>406.7901066731202</v>
+        <v>406.8167932745791</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33586,28 +33769,28 @@
         <v>0.1431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1273768595451887</v>
+        <v>0.1240033088865537</v>
       </c>
       <c r="J4" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K4" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07518350988780564</v>
+        <v>0.07204294681186951</v>
       </c>
       <c r="M4" t="n">
-        <v>2.5126295095706</v>
+        <v>2.519125495037688</v>
       </c>
       <c r="N4" t="n">
-        <v>11.6683876300915</v>
+        <v>11.6577865298035</v>
       </c>
       <c r="O4" t="n">
-        <v>3.415902169279955</v>
+        <v>3.414350088933983</v>
       </c>
       <c r="P4" t="n">
-        <v>397.9069060371181</v>
+        <v>397.9410495331969</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33664,28 +33847,28 @@
         <v>0.1071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1414801035420645</v>
+        <v>0.1348207459955639</v>
       </c>
       <c r="J5" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K5" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1126506857122586</v>
+        <v>0.1023977819383214</v>
       </c>
       <c r="M5" t="n">
-        <v>2.235218169518155</v>
+        <v>2.261261350865427</v>
       </c>
       <c r="N5" t="n">
-        <v>9.218246597022119</v>
+        <v>9.378210178219101</v>
       </c>
       <c r="O5" t="n">
-        <v>3.036156550150555</v>
+        <v>3.062386353518951</v>
       </c>
       <c r="P5" t="n">
-        <v>397.728608548727</v>
+        <v>397.7960048918937</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33742,28 +33925,28 @@
         <v>0.1192</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0920135484767934</v>
+        <v>0.0851616725907996</v>
       </c>
       <c r="J6" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K6" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03661297237281913</v>
+        <v>0.03138043363924092</v>
       </c>
       <c r="M6" t="n">
-        <v>2.862487655462854</v>
+        <v>2.889297676671264</v>
       </c>
       <c r="N6" t="n">
-        <v>13.02465326293287</v>
+        <v>13.17637068314296</v>
       </c>
       <c r="O6" t="n">
-        <v>3.608968448592045</v>
+        <v>3.629927090609805</v>
       </c>
       <c r="P6" t="n">
-        <v>397.2661374828631</v>
+        <v>397.3354891914097</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33820,28 +34003,28 @@
         <v>0.1403</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1436693630505506</v>
+        <v>0.1337624416373159</v>
       </c>
       <c r="J7" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K7" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06030084799834001</v>
+        <v>0.05207873924086703</v>
       </c>
       <c r="M7" t="n">
-        <v>3.42507399659542</v>
+        <v>3.449962876449037</v>
       </c>
       <c r="N7" t="n">
-        <v>18.80574545648377</v>
+        <v>19.16872908466871</v>
       </c>
       <c r="O7" t="n">
-        <v>4.336559172487304</v>
+        <v>4.378210717252964</v>
       </c>
       <c r="P7" t="n">
-        <v>398.9612539451352</v>
+        <v>399.0615229374745</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33898,28 +34081,28 @@
         <v>0.1456</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1043852307788729</v>
+        <v>0.09611211965339955</v>
       </c>
       <c r="J8" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K8" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02607691747413199</v>
+        <v>0.02216541725958754</v>
       </c>
       <c r="M8" t="n">
-        <v>3.713003840662262</v>
+        <v>3.726551999173769</v>
       </c>
       <c r="N8" t="n">
-        <v>23.79267778762085</v>
+        <v>23.98606102447032</v>
       </c>
       <c r="O8" t="n">
-        <v>4.877773855727717</v>
+        <v>4.897556638209539</v>
       </c>
       <c r="P8" t="n">
-        <v>399.3436015150625</v>
+        <v>399.4273336330642</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33976,28 +34159,28 @@
         <v>0.1405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08049745571081129</v>
+        <v>0.07308156040801832</v>
       </c>
       <c r="J9" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K9" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01309158513014297</v>
+        <v>0.01084890278237083</v>
       </c>
       <c r="M9" t="n">
-        <v>4.012596451159832</v>
+        <v>4.02568069878056</v>
       </c>
       <c r="N9" t="n">
-        <v>28.55917981436506</v>
+        <v>28.6619401702329</v>
       </c>
       <c r="O9" t="n">
-        <v>5.344078949114156</v>
+        <v>5.353684728318703</v>
       </c>
       <c r="P9" t="n">
-        <v>398.8971429324146</v>
+        <v>398.9721970449874</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34054,28 +34237,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04272778736935113</v>
+        <v>0.03357455594060813</v>
       </c>
       <c r="J10" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K10" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003799586961604984</v>
+        <v>0.00234486481102758</v>
       </c>
       <c r="M10" t="n">
-        <v>4.221891654910455</v>
+        <v>4.247920358057439</v>
       </c>
       <c r="N10" t="n">
-        <v>27.98516949709461</v>
+        <v>28.22905435440649</v>
       </c>
       <c r="O10" t="n">
-        <v>5.290101085716095</v>
+        <v>5.31310214040785</v>
       </c>
       <c r="P10" t="n">
-        <v>401.2934246751154</v>
+        <v>401.3860682104504</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -34136,28 +34319,28 @@
         <v>0.1537</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.05816694201046513</v>
+        <v>-0.06838722742124885</v>
       </c>
       <c r="J11" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K11" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002907180683864086</v>
+        <v>0.004033887770501621</v>
       </c>
       <c r="M11" t="n">
-        <v>6.461618336550289</v>
+        <v>6.483937606135719</v>
       </c>
       <c r="N11" t="n">
-        <v>67.84421697681422</v>
+        <v>67.96477543789985</v>
       </c>
       <c r="O11" t="n">
-        <v>8.236760101934147</v>
+        <v>8.244075171776386</v>
       </c>
       <c r="P11" t="n">
-        <v>392.6137490891191</v>
+        <v>392.7171923331408</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -34218,28 +34401,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.07575003568281688</v>
+        <v>-0.09298877700870047</v>
       </c>
       <c r="J12" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K12" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002526343211242676</v>
+        <v>0.00380828912283071</v>
       </c>
       <c r="M12" t="n">
-        <v>9.401300224302052</v>
+        <v>9.431875070998327</v>
       </c>
       <c r="N12" t="n">
-        <v>132.4559809450228</v>
+        <v>133.1334619558052</v>
       </c>
       <c r="O12" t="n">
-        <v>11.50895220882522</v>
+        <v>11.53834745341833</v>
       </c>
       <c r="P12" t="n">
-        <v>390.9870668982156</v>
+        <v>391.1615420361898</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -34300,28 +34483,28 @@
         <v>0.0965</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1648850904742679</v>
+        <v>-0.1857209063663363</v>
       </c>
       <c r="J13" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K13" t="n">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00865420124250027</v>
+        <v>0.01096492445509523</v>
       </c>
       <c r="M13" t="n">
-        <v>11.18914259794253</v>
+        <v>11.21753187091838</v>
       </c>
       <c r="N13" t="n">
-        <v>181.3768330373213</v>
+        <v>182.4172271510161</v>
       </c>
       <c r="O13" t="n">
-        <v>13.46762165481795</v>
+        <v>13.50619217807211</v>
       </c>
       <c r="P13" t="n">
-        <v>397.3880020599695</v>
+        <v>397.5996595445823</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -34382,28 +34565,28 @@
         <v>0.1218</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1635284683101995</v>
+        <v>-0.1763177461570902</v>
       </c>
       <c r="J14" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K14" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01557066328706724</v>
+        <v>0.01813424524346818</v>
       </c>
       <c r="M14" t="n">
-        <v>7.889709251929806</v>
+        <v>7.899500842129874</v>
       </c>
       <c r="N14" t="n">
-        <v>98.29495072001349</v>
+        <v>98.52275063488004</v>
       </c>
       <c r="O14" t="n">
-        <v>9.914381005388762</v>
+        <v>9.925862714891842</v>
       </c>
       <c r="P14" t="n">
-        <v>389.5454628092884</v>
+        <v>389.675456576399</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -34445,7 +34628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O537"/>
+  <dimension ref="A1:O540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75777,6 +75960,237 @@
         </is>
       </c>
     </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>-35.006941404093574,173.77984733919155</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>-35.006740923995196,173.7806277991365</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>-35.00649801715256,173.78142187845188</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>-35.006226784089534,173.78226339565717</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>-35.00591920799122,173.7830759891048</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>-35.00561905180473,173.7838823170646</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>-35.005259064624006,173.78462936028092</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>-35.004852741583996,173.78534306272354</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>-35.00441140802832,173.7859919262845</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>-35.003911018686644,173.7866134880755</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>-35.003385748594575,173.78727606597235</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>-35.00294548607858,173.7880093649544</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>-35.00252891345571,173.7887380359323</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>-35.00693177166714,173.77984496575587</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>-35.006742113387475,173.78062831320412</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>-35.006501347256794,173.7814238297228</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>-35.00622817332562,173.78226418303166</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>-35.00592474300975,173.78307919511315</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>-35.0056184924531,173.78388196165747</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>-35.005259064624006,173.78462936028092</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>-35.00485088920688,173.78534131631895</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>-35.004414428656645,173.78599584506097</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>-35.003913518543435,173.78661737235535</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>-35.00338962176692,173.78728049824346</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>-35.00294359685151,173.78800767790472</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>-35.00251568846302,173.78872622731458</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>-35.006925408963404,173.77984339798215</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>-35.0067369310354,173.78062607333834</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>-35.00649801715256,173.78142187845188</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>-35.00622376045802,173.78226168195985</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>-35.005927184929654,173.78308060952875</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>-35.00562512476518,173.78388617577102</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>-35.005262318537476,173.7846319226763</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>-35.004852741583996,173.78534306272354</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>-35.00441831232143,173.7860008834882</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>-35.003917684971135,173.78662384615566</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>-35.0033931010572,173.78728447977548</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>-35.00294737530562,173.78801105200412</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>-35.002517069094196,173.78872746008219</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0045/nzd0045.xlsx
+++ b/data/nzd0045/nzd0045.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O540"/>
+  <dimension ref="A1:O543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27982,6 +27982,159 @@
         <v>373.79</v>
       </c>
       <c r="O540" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>400.68</v>
+      </c>
+      <c r="C541" t="n">
+        <v>407.75</v>
+      </c>
+      <c r="D541" t="n">
+        <v>398.04</v>
+      </c>
+      <c r="E541" t="n">
+        <v>395.62</v>
+      </c>
+      <c r="F541" t="n">
+        <v>392.8</v>
+      </c>
+      <c r="G541" t="n">
+        <v>392.85</v>
+      </c>
+      <c r="H541" t="n">
+        <v>393.93</v>
+      </c>
+      <c r="I541" t="n">
+        <v>393.76</v>
+      </c>
+      <c r="J541" t="n">
+        <v>393.14</v>
+      </c>
+      <c r="K541" t="n">
+        <v>380.09</v>
+      </c>
+      <c r="L541" t="n">
+        <v>371.74</v>
+      </c>
+      <c r="M541" t="n">
+        <v>373.01</v>
+      </c>
+      <c r="N541" t="n">
+        <v>374.3</v>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>401.72</v>
+      </c>
+      <c r="C542" t="n">
+        <v>408.2</v>
+      </c>
+      <c r="D542" t="n">
+        <v>398.2</v>
+      </c>
+      <c r="E542" t="n">
+        <v>395.11</v>
+      </c>
+      <c r="F542" t="n">
+        <v>392.31</v>
+      </c>
+      <c r="G542" t="n">
+        <v>392.69</v>
+      </c>
+      <c r="H542" t="n">
+        <v>393.46</v>
+      </c>
+      <c r="I542" t="n">
+        <v>393.12</v>
+      </c>
+      <c r="J542" t="n">
+        <v>392.65</v>
+      </c>
+      <c r="K542" t="n">
+        <v>378.73</v>
+      </c>
+      <c r="L542" t="n">
+        <v>370.62</v>
+      </c>
+      <c r="M542" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="N542" t="n">
+        <v>375.09</v>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>402.4</v>
+      </c>
+      <c r="C543" t="n">
+        <v>408.7</v>
+      </c>
+      <c r="D543" t="n">
+        <v>398.56</v>
+      </c>
+      <c r="E543" t="n">
+        <v>395.76</v>
+      </c>
+      <c r="F543" t="n">
+        <v>392.36</v>
+      </c>
+      <c r="G543" t="n">
+        <v>392.99</v>
+      </c>
+      <c r="H543" t="n">
+        <v>393.74</v>
+      </c>
+      <c r="I543" t="n">
+        <v>393.25</v>
+      </c>
+      <c r="J543" t="n">
+        <v>392.55</v>
+      </c>
+      <c r="K543" t="n">
+        <v>378.55</v>
+      </c>
+      <c r="L543" t="n">
+        <v>369.89</v>
+      </c>
+      <c r="M543" t="n">
+        <v>372.42</v>
+      </c>
+      <c r="N543" t="n">
+        <v>374.49</v>
+      </c>
+      <c r="O543" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27998,7 +28151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B544"/>
+  <dimension ref="A1:B547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33441,6 +33594,36 @@
       </c>
       <c r="B544" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -33609,28 +33792,28 @@
         <v>0.1432</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1353961822308057</v>
+        <v>0.1345511456412014</v>
       </c>
       <c r="J2" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K2" t="n">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0489246743494417</v>
+        <v>0.04889419067336831</v>
       </c>
       <c r="M2" t="n">
-        <v>3.416280224128933</v>
+        <v>3.401870255761955</v>
       </c>
       <c r="N2" t="n">
-        <v>21.01187502696801</v>
+        <v>20.90156473563465</v>
       </c>
       <c r="O2" t="n">
-        <v>4.583871183505052</v>
+        <v>4.571822911666051</v>
       </c>
       <c r="P2" t="n">
-        <v>398.7800803269538</v>
+        <v>398.7886488202862</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33691,28 +33874,28 @@
         <v>0.1717</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1258218625197281</v>
+        <v>0.1237432161034667</v>
       </c>
       <c r="J3" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K3" t="n">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04533320240231387</v>
+        <v>0.04437917445828132</v>
       </c>
       <c r="M3" t="n">
-        <v>3.352713591817678</v>
+        <v>3.347166456733509</v>
       </c>
       <c r="N3" t="n">
-        <v>19.65679186276278</v>
+        <v>19.56958482032962</v>
       </c>
       <c r="O3" t="n">
-        <v>4.433598071855723</v>
+        <v>4.423752346179612</v>
       </c>
       <c r="P3" t="n">
-        <v>406.8167932745791</v>
+        <v>406.8378827207906</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33769,28 +33952,28 @@
         <v>0.1431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1240033088865537</v>
+        <v>0.1208380218445359</v>
       </c>
       <c r="J4" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K4" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07204294681186951</v>
+        <v>0.06917293145499537</v>
       </c>
       <c r="M4" t="n">
-        <v>2.519125495037688</v>
+        <v>2.524336427668017</v>
       </c>
       <c r="N4" t="n">
-        <v>11.6577865298035</v>
+        <v>11.64200772222418</v>
       </c>
       <c r="O4" t="n">
-        <v>3.414350088933983</v>
+        <v>3.412038646062523</v>
       </c>
       <c r="P4" t="n">
-        <v>397.9410495331969</v>
+        <v>397.9731891735257</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33847,28 +34030,28 @@
         <v>0.1071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1348207459955639</v>
+        <v>0.1285620336167519</v>
       </c>
       <c r="J5" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K5" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1023977819383214</v>
+        <v>0.0933053589638646</v>
       </c>
       <c r="M5" t="n">
-        <v>2.261261350865427</v>
+        <v>2.285321185392094</v>
       </c>
       <c r="N5" t="n">
-        <v>9.378210178219101</v>
+        <v>9.516292304870156</v>
       </c>
       <c r="O5" t="n">
-        <v>3.062386353518951</v>
+        <v>3.084848830148757</v>
       </c>
       <c r="P5" t="n">
-        <v>397.7960048918937</v>
+        <v>397.8595578774245</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33925,28 +34108,28 @@
         <v>0.1192</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0851616725907996</v>
+        <v>0.07761477444575374</v>
       </c>
       <c r="J6" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K6" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03138043363924092</v>
+        <v>0.02598419963588716</v>
       </c>
       <c r="M6" t="n">
-        <v>2.889297676671264</v>
+        <v>2.920422036713723</v>
       </c>
       <c r="N6" t="n">
-        <v>13.17637068314296</v>
+        <v>13.37929725341786</v>
       </c>
       <c r="O6" t="n">
-        <v>3.629927090609805</v>
+        <v>3.65777217079165</v>
       </c>
       <c r="P6" t="n">
-        <v>397.3354891914097</v>
+        <v>397.4121250563155</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34003,28 +34186,28 @@
         <v>0.1403</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1337624416373159</v>
+        <v>0.1233813800205643</v>
       </c>
       <c r="J7" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K7" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05207873924086703</v>
+        <v>0.04402773624159628</v>
       </c>
       <c r="M7" t="n">
-        <v>3.449962876449037</v>
+        <v>3.479063752645628</v>
       </c>
       <c r="N7" t="n">
-        <v>19.16872908466871</v>
+        <v>19.58420869608141</v>
       </c>
       <c r="O7" t="n">
-        <v>4.378210717252964</v>
+        <v>4.425404918883854</v>
       </c>
       <c r="P7" t="n">
-        <v>399.0615229374745</v>
+        <v>399.1669358211407</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34081,28 +34264,28 @@
         <v>0.1456</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09611211965339955</v>
+        <v>0.08732914257171259</v>
       </c>
       <c r="J8" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K8" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02216541725958754</v>
+        <v>0.01830985515616057</v>
       </c>
       <c r="M8" t="n">
-        <v>3.726551999173769</v>
+        <v>3.742600537732032</v>
       </c>
       <c r="N8" t="n">
-        <v>23.98606102447032</v>
+        <v>24.22678360463307</v>
       </c>
       <c r="O8" t="n">
-        <v>4.897556638209539</v>
+        <v>4.922071068628842</v>
       </c>
       <c r="P8" t="n">
-        <v>399.4273336330642</v>
+        <v>399.5165201813344</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34159,28 +34342,28 @@
         <v>0.1405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07308156040801832</v>
+        <v>0.06507842403623777</v>
       </c>
       <c r="J9" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K9" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01084890278237083</v>
+        <v>0.008633718537305879</v>
       </c>
       <c r="M9" t="n">
-        <v>4.02568069878056</v>
+        <v>4.041264264086893</v>
       </c>
       <c r="N9" t="n">
-        <v>28.6619401702329</v>
+        <v>28.81364209694513</v>
       </c>
       <c r="O9" t="n">
-        <v>5.353684728318703</v>
+        <v>5.36783402285737</v>
       </c>
       <c r="P9" t="n">
-        <v>398.9721970449874</v>
+        <v>399.0534660287425</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34237,28 +34420,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03357455594060813</v>
+        <v>0.02349787926133601</v>
       </c>
       <c r="J10" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K10" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00234486481102758</v>
+        <v>0.001143988120690498</v>
       </c>
       <c r="M10" t="n">
-        <v>4.247920358057439</v>
+        <v>4.278833447879083</v>
       </c>
       <c r="N10" t="n">
-        <v>28.22905435440649</v>
+        <v>28.56449527133534</v>
       </c>
       <c r="O10" t="n">
-        <v>5.31310214040785</v>
+        <v>5.34457624806077</v>
       </c>
       <c r="P10" t="n">
-        <v>401.3860682104504</v>
+        <v>401.4883929993131</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -34319,28 +34502,28 @@
         <v>0.1537</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.06838722742124885</v>
+        <v>-0.08086061436795591</v>
       </c>
       <c r="J11" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K11" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004033887770501621</v>
+        <v>0.005636466788397354</v>
       </c>
       <c r="M11" t="n">
-        <v>6.483937606135719</v>
+        <v>6.518664814692237</v>
       </c>
       <c r="N11" t="n">
-        <v>67.96477543789985</v>
+        <v>68.34396255801246</v>
       </c>
       <c r="O11" t="n">
-        <v>8.244075171776386</v>
+        <v>8.267040737652891</v>
       </c>
       <c r="P11" t="n">
-        <v>392.7171923331408</v>
+        <v>392.8438578771455</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -34401,28 +34584,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.09298877700870047</v>
+        <v>-0.1119933380393922</v>
       </c>
       <c r="J12" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K12" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00380828912283071</v>
+        <v>0.005509234079338121</v>
       </c>
       <c r="M12" t="n">
-        <v>9.431875070998327</v>
+        <v>9.470277329344482</v>
       </c>
       <c r="N12" t="n">
-        <v>133.1334619558052</v>
+        <v>134.1472437060089</v>
       </c>
       <c r="O12" t="n">
-        <v>11.53834745341833</v>
+        <v>11.58219511603948</v>
       </c>
       <c r="P12" t="n">
-        <v>391.1615420361898</v>
+        <v>391.3545287650219</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -34483,28 +34666,28 @@
         <v>0.0965</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1857209063663363</v>
+        <v>-0.2067890017340167</v>
       </c>
       <c r="J13" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K13" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01096492445509523</v>
+        <v>0.01356459452046888</v>
       </c>
       <c r="M13" t="n">
-        <v>11.21753187091838</v>
+        <v>11.25007512406545</v>
       </c>
       <c r="N13" t="n">
-        <v>182.4172271510161</v>
+        <v>183.5398994399048</v>
       </c>
       <c r="O13" t="n">
-        <v>13.50619217807211</v>
+        <v>13.54768981929779</v>
       </c>
       <c r="P13" t="n">
-        <v>397.5996595445823</v>
+        <v>397.8143879665503</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -34565,28 +34748,28 @@
         <v>0.1218</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1763177461570902</v>
+        <v>-0.1873315080674169</v>
       </c>
       <c r="J14" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K14" t="n">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01813424524346818</v>
+        <v>0.02054855989514681</v>
       </c>
       <c r="M14" t="n">
-        <v>7.899500842129874</v>
+        <v>7.901750543072283</v>
       </c>
       <c r="N14" t="n">
-        <v>98.52275063488004</v>
+        <v>98.55939426507497</v>
       </c>
       <c r="O14" t="n">
-        <v>9.925862714891842</v>
+        <v>9.927708409551268</v>
       </c>
       <c r="P14" t="n">
-        <v>389.675456576399</v>
+        <v>389.7877818170095</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -34628,7 +34811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O540"/>
+  <dimension ref="A1:O543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76191,6 +76374,237 @@
         </is>
       </c>
     </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>-35.006926292672254,173.77984361572848</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>-35.0067399894727,173.7806273952263</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>-35.00650004770392,173.7814230682512</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>-35.006223515298714,173.7822615430114</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>-35.005927998902955,173.78308108100063</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>-35.00562648319054,173.78388703890278</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>-35.00526375631317,173.7846330548976</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>-35.00485473645165,173.78534494346707</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>-35.00441936029444,173.78600224306388</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>-35.00392207360793,173.78663066522603</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>-35.00339703987621,173.78728898717063</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>-35.002950136483555,173.78801351769238</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>-35.002513363189465,173.7887241510745</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>-35.00691710210015,173.77984135116682</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>-35.00673616642608,173.78062574286633</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>-35.00649874815105,173.7814223067796</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-35.006227683007005,173.78226390513476</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>-35.00593198737208,173.78308339121298</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>-35.00562776170852,173.78388785126214</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>-35.005267312916175,173.7846358556557</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>-35.004859296149,173.7853492423097</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>-35.0044223809224,173.7860061618411</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>-35.00392962872858,173.7866424043868</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>-35.00340439233789,173.78729740097606</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>-35.002949191870066,173.78801267416745</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>-35.00250762267019,173.7887190253573</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>-35.006911092879875,173.7798398704922</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>-35.00673191859649,173.78062390691105</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>-35.006495824157064,173.78142059346868</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-35.006222371221924,173.78226089458542</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>-35.005931580385436,173.78308315547702</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>-35.005625364487315,173.78388632808839</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>-35.005265194088864,173.78463418711894</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>-35.004858369960495,173.78534836910725</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>-35.00442299737707,173.78600696159157</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>-35.00393062867092,173.78664395809943</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>-35.00340918456706,173.78730288497508</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>-35.00295442357551,173.78801734599816</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>-35.002511982558254,173.78872291830697</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0045/nzd0045.xlsx
+++ b/data/nzd0045/nzd0045.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O543"/>
+  <dimension ref="A1:O547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28135,6 +28135,210 @@
         <v>374.49</v>
       </c>
       <c r="O543" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>402.52</v>
+      </c>
+      <c r="C544" t="n">
+        <v>408.09</v>
+      </c>
+      <c r="D544" t="n">
+        <v>397.99</v>
+      </c>
+      <c r="E544" t="n">
+        <v>394.64</v>
+      </c>
+      <c r="F544" t="n">
+        <v>391.37</v>
+      </c>
+      <c r="G544" t="n">
+        <v>392.37</v>
+      </c>
+      <c r="H544" t="n">
+        <v>392.95</v>
+      </c>
+      <c r="I544" t="n">
+        <v>392.41</v>
+      </c>
+      <c r="J544" t="n">
+        <v>391.28</v>
+      </c>
+      <c r="K544" t="n">
+        <v>376.86</v>
+      </c>
+      <c r="L544" t="n">
+        <v>368.51</v>
+      </c>
+      <c r="M544" t="n">
+        <v>371.26</v>
+      </c>
+      <c r="N544" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>403.37</v>
+      </c>
+      <c r="C545" t="n">
+        <v>408.15</v>
+      </c>
+      <c r="D545" t="n">
+        <v>398.27</v>
+      </c>
+      <c r="E545" t="n">
+        <v>395.37</v>
+      </c>
+      <c r="F545" t="n">
+        <v>391.6</v>
+      </c>
+      <c r="G545" t="n">
+        <v>392.75</v>
+      </c>
+      <c r="H545" t="n">
+        <v>392.48</v>
+      </c>
+      <c r="I545" t="n">
+        <v>392.26</v>
+      </c>
+      <c r="J545" t="n">
+        <v>390.91</v>
+      </c>
+      <c r="K545" t="n">
+        <v>376.3</v>
+      </c>
+      <c r="L545" t="n">
+        <v>367.71</v>
+      </c>
+      <c r="M545" t="n">
+        <v>370.08</v>
+      </c>
+      <c r="N545" t="n">
+        <v>372.58</v>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>404.69</v>
+      </c>
+      <c r="C546" t="n">
+        <v>409.76</v>
+      </c>
+      <c r="D546" t="n">
+        <v>399.1</v>
+      </c>
+      <c r="E546" t="n">
+        <v>395.94</v>
+      </c>
+      <c r="F546" t="n">
+        <v>392.16</v>
+      </c>
+      <c r="G546" t="n">
+        <v>393.45</v>
+      </c>
+      <c r="H546" t="n">
+        <v>393.2</v>
+      </c>
+      <c r="I546" t="n">
+        <v>392.76</v>
+      </c>
+      <c r="J546" t="n">
+        <v>391.65</v>
+      </c>
+      <c r="K546" t="n">
+        <v>376.97</v>
+      </c>
+      <c r="L546" t="n">
+        <v>367.77</v>
+      </c>
+      <c r="M546" t="n">
+        <v>369.66</v>
+      </c>
+      <c r="N546" t="n">
+        <v>372.33</v>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>406.03</v>
+      </c>
+      <c r="C547" t="n">
+        <v>411.83</v>
+      </c>
+      <c r="D547" t="n">
+        <v>400.88</v>
+      </c>
+      <c r="E547" t="n">
+        <v>397.15</v>
+      </c>
+      <c r="F547" t="n">
+        <v>392.62</v>
+      </c>
+      <c r="G547" t="n">
+        <v>393.52</v>
+      </c>
+      <c r="H547" t="n">
+        <v>393.66</v>
+      </c>
+      <c r="I547" t="n">
+        <v>392.71</v>
+      </c>
+      <c r="J547" t="n">
+        <v>391.92</v>
+      </c>
+      <c r="K547" t="n">
+        <v>377.07</v>
+      </c>
+      <c r="L547" t="n">
+        <v>367.62</v>
+      </c>
+      <c r="M547" t="n">
+        <v>370.22</v>
+      </c>
+      <c r="N547" t="n">
+        <v>370.93</v>
+      </c>
+      <c r="O547" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28151,7 +28355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B547"/>
+  <dimension ref="A1:B551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33624,6 +33828,46 @@
       </c>
       <c r="B547" t="n">
         <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -33792,28 +34036,28 @@
         <v>0.1432</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1345511456412014</v>
+        <v>0.1369969460662765</v>
       </c>
       <c r="J2" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K2" t="n">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04889419067336831</v>
+        <v>0.05129041550397906</v>
       </c>
       <c r="M2" t="n">
-        <v>3.401870255761955</v>
+        <v>3.389264167321841</v>
       </c>
       <c r="N2" t="n">
-        <v>20.90156473563465</v>
+        <v>20.78327620667166</v>
       </c>
       <c r="O2" t="n">
-        <v>4.571822911666051</v>
+        <v>4.558867864576869</v>
       </c>
       <c r="P2" t="n">
-        <v>398.7886488202862</v>
+        <v>398.7637189954197</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33874,28 +34118,28 @@
         <v>0.1717</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1237432161034667</v>
+        <v>0.1227746388076638</v>
       </c>
       <c r="J3" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K3" t="n">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04437917445828132</v>
+        <v>0.04434773272268666</v>
       </c>
       <c r="M3" t="n">
-        <v>3.347166456733509</v>
+        <v>3.334814262602376</v>
       </c>
       <c r="N3" t="n">
-        <v>19.56958482032962</v>
+        <v>19.44647859554246</v>
       </c>
       <c r="O3" t="n">
-        <v>4.423752346179612</v>
+        <v>4.409816163463332</v>
       </c>
       <c r="P3" t="n">
-        <v>406.8378827207906</v>
+        <v>406.847736472676</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33952,28 +34196,28 @@
         <v>0.1431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1208380218445359</v>
+        <v>0.1178399842104849</v>
       </c>
       <c r="J4" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K4" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06917293145499537</v>
+        <v>0.06677321005621395</v>
       </c>
       <c r="M4" t="n">
-        <v>2.524336427668017</v>
+        <v>2.52418756144882</v>
       </c>
       <c r="N4" t="n">
-        <v>11.64200772222418</v>
+        <v>11.59926681966404</v>
       </c>
       <c r="O4" t="n">
-        <v>3.412038646062523</v>
+        <v>3.405769636905004</v>
       </c>
       <c r="P4" t="n">
-        <v>397.9731891735257</v>
+        <v>398.0037421212191</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34030,28 +34274,28 @@
         <v>0.1071</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1285620336167519</v>
+        <v>0.1208684422016891</v>
       </c>
       <c r="J5" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K5" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0933053589638646</v>
+        <v>0.08280373658570517</v>
       </c>
       <c r="M5" t="n">
-        <v>2.285321185392094</v>
+        <v>2.313848671209308</v>
       </c>
       <c r="N5" t="n">
-        <v>9.516292304870156</v>
+        <v>9.671602440294309</v>
       </c>
       <c r="O5" t="n">
-        <v>3.084848830148757</v>
+        <v>3.109920005449386</v>
       </c>
       <c r="P5" t="n">
-        <v>397.8595578774245</v>
+        <v>397.9379811711758</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34108,28 +34352,28 @@
         <v>0.1192</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07761477444575374</v>
+        <v>0.06709904024825875</v>
       </c>
       <c r="J6" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K6" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02598419963588716</v>
+        <v>0.01927429708234485</v>
       </c>
       <c r="M6" t="n">
-        <v>2.920422036713723</v>
+        <v>2.965121571632963</v>
       </c>
       <c r="N6" t="n">
-        <v>13.37929725341786</v>
+        <v>13.69184172975892</v>
       </c>
       <c r="O6" t="n">
-        <v>3.65777217079165</v>
+        <v>3.700248874029816</v>
       </c>
       <c r="P6" t="n">
-        <v>397.4121250563155</v>
+        <v>397.519323143881</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34186,28 +34430,28 @@
         <v>0.1403</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1233813800205643</v>
+        <v>0.1102296113280878</v>
       </c>
       <c r="J7" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K7" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04402773624159628</v>
+        <v>0.03489995623520414</v>
       </c>
       <c r="M7" t="n">
-        <v>3.479063752645628</v>
+        <v>3.518098060625705</v>
       </c>
       <c r="N7" t="n">
-        <v>19.58420869608141</v>
+        <v>20.0818745642212</v>
       </c>
       <c r="O7" t="n">
-        <v>4.425404918883854</v>
+        <v>4.481280460339566</v>
       </c>
       <c r="P7" t="n">
-        <v>399.1669358211407</v>
+        <v>399.3010073659659</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34264,28 +34508,28 @@
         <v>0.1456</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08732914257171259</v>
+        <v>0.07510758087273758</v>
       </c>
       <c r="J8" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K8" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01830985515616057</v>
+        <v>0.01351861108381081</v>
       </c>
       <c r="M8" t="n">
-        <v>3.742600537732032</v>
+        <v>3.766535431754627</v>
       </c>
       <c r="N8" t="n">
-        <v>24.22678360463307</v>
+        <v>24.60280448056614</v>
       </c>
       <c r="O8" t="n">
-        <v>4.922071068628842</v>
+        <v>4.960121417925789</v>
       </c>
       <c r="P8" t="n">
-        <v>399.5165201813344</v>
+        <v>399.6411101215412</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34342,28 +34586,28 @@
         <v>0.1405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06507842403623777</v>
+        <v>0.05358190263636256</v>
       </c>
       <c r="J9" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K9" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008633718537305879</v>
+        <v>0.00586377018501183</v>
       </c>
       <c r="M9" t="n">
-        <v>4.041264264086893</v>
+        <v>4.066119670529052</v>
       </c>
       <c r="N9" t="n">
-        <v>28.81364209694513</v>
+        <v>29.09145661751428</v>
       </c>
       <c r="O9" t="n">
-        <v>5.36783402285737</v>
+        <v>5.393649656541875</v>
       </c>
       <c r="P9" t="n">
-        <v>399.0534660287425</v>
+        <v>399.1706661427346</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34420,28 +34664,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02349787926133601</v>
+        <v>0.008637104823229172</v>
       </c>
       <c r="J10" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K10" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001143988120690498</v>
+        <v>0.0001528107059969308</v>
       </c>
       <c r="M10" t="n">
-        <v>4.278833447879083</v>
+        <v>4.328139367092451</v>
       </c>
       <c r="N10" t="n">
-        <v>28.56449527133534</v>
+        <v>29.1726897669173</v>
       </c>
       <c r="O10" t="n">
-        <v>5.34457624806077</v>
+        <v>5.401174850615123</v>
       </c>
       <c r="P10" t="n">
-        <v>401.4883929993131</v>
+        <v>401.6398886430646</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -34502,28 +34746,28 @@
         <v>0.1537</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08086061436795591</v>
+        <v>-0.1001678298760016</v>
       </c>
       <c r="J11" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K11" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005636466788397354</v>
+        <v>0.008588693975554285</v>
       </c>
       <c r="M11" t="n">
-        <v>6.518664814692237</v>
+        <v>6.579358221314632</v>
       </c>
       <c r="N11" t="n">
-        <v>68.34396255801246</v>
+        <v>69.22189965205519</v>
       </c>
       <c r="O11" t="n">
-        <v>8.267040737652891</v>
+        <v>8.319969930958596</v>
       </c>
       <c r="P11" t="n">
-        <v>392.8438578771455</v>
+        <v>393.0406842607768</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -34584,28 +34828,28 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1119933380393922</v>
+        <v>-0.1404453885726913</v>
       </c>
       <c r="J12" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K12" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005509234079338121</v>
+        <v>0.008583987875846799</v>
       </c>
       <c r="M12" t="n">
-        <v>9.470277329344482</v>
+        <v>9.537628381181317</v>
       </c>
       <c r="N12" t="n">
-        <v>134.1472437060089</v>
+        <v>136.1576497051007</v>
       </c>
       <c r="O12" t="n">
-        <v>11.58219511603948</v>
+        <v>11.66866100737787</v>
       </c>
       <c r="P12" t="n">
-        <v>391.3545287650219</v>
+        <v>391.6445861813598</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -34666,28 +34910,28 @@
         <v>0.0965</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2067890017340167</v>
+        <v>-0.2374970058633547</v>
       </c>
       <c r="J13" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K13" t="n">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01356459452046888</v>
+        <v>0.01776654477602035</v>
       </c>
       <c r="M13" t="n">
-        <v>11.25007512406545</v>
+        <v>11.30751266825498</v>
       </c>
       <c r="N13" t="n">
-        <v>183.5398994399048</v>
+        <v>185.6586359452176</v>
       </c>
       <c r="O13" t="n">
-        <v>13.54768981929779</v>
+        <v>13.62566093608738</v>
       </c>
       <c r="P13" t="n">
-        <v>397.8143879665503</v>
+        <v>398.1286017665648</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -34748,28 +34992,28 @@
         <v>0.1218</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1873315080674169</v>
+        <v>-0.2048391797681091</v>
       </c>
       <c r="J14" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K14" t="n">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02054855989514681</v>
+        <v>0.02458074402141319</v>
       </c>
       <c r="M14" t="n">
-        <v>7.901750543072283</v>
+        <v>7.919879615379386</v>
       </c>
       <c r="N14" t="n">
-        <v>98.55939426507497</v>
+        <v>98.96472299429161</v>
       </c>
       <c r="O14" t="n">
-        <v>9.927708409551268</v>
+        <v>9.948101476879476</v>
       </c>
       <c r="P14" t="n">
-        <v>389.7877818170095</v>
+        <v>389.9670471449923</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -34811,7 +35055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O543"/>
+  <dimension ref="A1:O547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76605,6 +76849,314 @@
         </is>
       </c>
     </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>-35.00691003242925,173.7798396091967</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>-35.00673710094859,173.78062614677654</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>-35.006500453814205,173.78142330621108</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-35.006231523836156,173.78226608199375</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>-35.00593963872088,173.78308782304958</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>-35.00563031874443,173.78388947598089</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>-35.00527117220872,173.78463889477646</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>-35.004864354563054,173.78535401133882</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>-35.00443082635094,173.7860171184237</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>-35.00394001701754,173.78665854573643</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>-35.00341824384888,173.7873132519886</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>-35.00296285243391,173.78802487283778</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>-35.002521792305956,173.78873167744536</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>-35.006902520903864,173.77983775835378</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>-35.006736591209034,173.7806259264619</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>-35.00649817959666,173.78142197363582</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-35.00622555829299,173.782262700915</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>-35.00593776658236,173.78308673866397</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>-35.00562728226427,173.78388754662737</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>-35.00527472881157,173.78464169553507</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>-35.00486542324206,173.78535501888027</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>-35.00443310723293,173.78602007750115</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>-35.00394312794856,173.78666337951037</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>-35.00342349560603,173.7873192618526</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>-35.00297142661694,173.78803252945212</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>-35.002525861534416,173.78873531086634</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>-35.00689085594673,173.77983488410428</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>-35.00672291319762,173.7806200146864</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>-35.00649143816604,173.78141802350245</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>-35.00622090026603,173.7822600608949</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>-35.00593320833201,173.78308409842091</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>-35.0056216887481,173.78388399255547</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>-35.00526928039866,173.78463740501135</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>-35.00486186097868,173.7853516604089</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>-35.00442854546889,173.78601415934642</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>-35.003939405941786,173.78665759624516</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>-35.00342310172425,173.78731881111275</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>-35.00297447844466,173.78803525468814</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>-35.00252767815424,173.78873693292937</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>-35.006879014247716,173.7798319663064</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>-35.006705327182445,173.78061241383517</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>-35.006476980639604,173.7814095521343</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-35.006211012173544,173.78225445664276</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>-35.00592946405488,173.78308192965005</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>-35.00562112939647,173.7838836371483</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>-35.0052657994681,173.7846346638437</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>-35.00486221720502,173.78535199625603</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>-35.00442688104138,173.78601200001987</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>-35.00393885041835,173.7866567330713</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>-35.00342408642868,173.78731993796234</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>-35.002970409341,173.78803162104018</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>-35.00253785122479,173.7887460164838</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
